--- a/Datos/registros_ergonomicos.xlsx
+++ b/Datos/registros_ergonomicos.xlsx
@@ -463,10 +463,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.5</v>
+        <v>12.2</v>
       </c>
       <c r="C2" t="n">
-        <v>1660</v>
+        <v>3892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.6</v>
+        <v>12.2</v>
       </c>
       <c r="C3" t="n">
-        <v>2969</v>
+        <v>1130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -505,18 +505,18 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-10.1</v>
+        <v>18.3</v>
       </c>
       <c r="C4" t="n">
-        <v>74</v>
+        <v>2282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
@@ -526,18 +526,18 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.5</v>
+        <v>27.1</v>
       </c>
       <c r="C5" t="n">
-        <v>130</v>
+        <v>930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.2</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -568,18 +568,18 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6</v>
+        <v>13.1</v>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>3653</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-14.3</v>
+        <v>9.4</v>
       </c>
       <c r="C8" t="n">
-        <v>821</v>
+        <v>3233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="9">
@@ -610,18 +610,18 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>9.4</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>1259</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -631,10 +631,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-2.7</v>
+        <v>-14.3</v>
       </c>
       <c r="C10" t="n">
-        <v>3534</v>
+        <v>821</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="11">
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32.8</v>
+        <v>22.2</v>
       </c>
       <c r="C11" t="n">
-        <v>2328</v>
+        <v>2847</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -673,18 +673,18 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-2.6</v>
+        <v>6.6</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>3547</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="13">
@@ -694,18 +694,18 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9.6</v>
+        <v>-10.7</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>3534</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13.3</v>
+        <v>15.8</v>
       </c>
       <c r="C14" t="n">
-        <v>1041</v>
+        <v>3805</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="15">
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14.6</v>
+        <v>-2.1</v>
       </c>
       <c r="C15" t="n">
-        <v>2939</v>
+        <v>3679</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.6</v>
+        <v>16.5</v>
       </c>
       <c r="C16" t="n">
-        <v>2278</v>
+        <v>2328</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="17">
@@ -778,18 +778,18 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>80</v>
+        <v>2868</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -799,10 +799,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1.5</v>
+        <v>7.8</v>
       </c>
       <c r="C18" t="n">
-        <v>3873</v>
+        <v>3688</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="19">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10.8</v>
+        <v>11.5</v>
       </c>
       <c r="C19" t="n">
-        <v>2300</v>
+        <v>2163</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-11.1</v>
+        <v>2.7</v>
       </c>
       <c r="C20" t="n">
-        <v>3577</v>
+        <v>2939</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="21">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.5</v>
+        <v>13.1</v>
       </c>
       <c r="C21" t="n">
-        <v>1615</v>
+        <v>3356</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13.6</v>
+        <v>24.9</v>
       </c>
       <c r="C22" t="n">
-        <v>2075</v>
+        <v>1575</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="23">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11.4</v>
+        <v>0.3</v>
       </c>
       <c r="C23" t="n">
-        <v>1137</v>
+        <v>3873</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.2</v>
+        <v>48.3</v>
       </c>
       <c r="C24" t="n">
-        <v>1591</v>
+        <v>1821</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="25">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.4</v>
+        <v>29.3</v>
       </c>
       <c r="C25" t="n">
-        <v>3912</v>
+        <v>2300</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14.5</v>
+        <v>12.9</v>
       </c>
       <c r="C26" t="n">
-        <v>864</v>
+        <v>1502</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="27">
@@ -988,10 +988,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11.7</v>
+        <v>29.4</v>
       </c>
       <c r="C27" t="n">
-        <v>3495</v>
+        <v>1001</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.2</v>
+        <v>17.1</v>
       </c>
       <c r="C28" t="n">
-        <v>138</v>
+        <v>2781</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="29">
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.1</v>
+        <v>18.9</v>
       </c>
       <c r="C29" t="n">
-        <v>1178</v>
+        <v>1255</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -1051,18 +1051,18 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-4.5</v>
+        <v>13.6</v>
       </c>
       <c r="C30" t="n">
-        <v>40</v>
+        <v>2075</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="31">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>13.7</v>
+        <v>11.4</v>
       </c>
       <c r="C31" t="n">
-        <v>2551</v>
+        <v>3567</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>25</v>
+        <v>43.1</v>
       </c>
       <c r="C32" t="n">
-        <v>3531</v>
+        <v>1137</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="33">
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>18.6</v>
+        <v>27.9</v>
       </c>
       <c r="C33" t="n">
-        <v>3460</v>
+        <v>3064</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19.3</v>
+        <v>-3.1</v>
       </c>
       <c r="C34" t="n">
-        <v>3490</v>
+        <v>1563</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="35">
@@ -1156,10 +1156,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>33.5</v>
+        <v>23.7</v>
       </c>
       <c r="C35" t="n">
-        <v>1670</v>
+        <v>1980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36">
@@ -1177,18 +1177,18 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8</v>
+        <v>-7.5</v>
       </c>
       <c r="C36" t="n">
-        <v>14</v>
+        <v>2862</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="37">
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.4</v>
+        <v>-1.4</v>
       </c>
       <c r="C37" t="n">
-        <v>1663</v>
+        <v>3495</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>36.5</v>
+        <v>26.2</v>
       </c>
       <c r="C38" t="n">
-        <v>1363</v>
+        <v>2295</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="39">
@@ -1240,18 +1240,18 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.9</v>
+        <v>23.1</v>
       </c>
       <c r="C39" t="n">
-        <v>142</v>
+        <v>1178</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>16.6</v>
+        <v>17.5</v>
       </c>
       <c r="C40" t="n">
-        <v>1859</v>
+        <v>2596</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="41">
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="C41" t="n">
-        <v>2619</v>
+        <v>3899</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
@@ -1303,10 +1303,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7.7</v>
+        <v>13</v>
       </c>
       <c r="C42" t="n">
-        <v>3404</v>
+        <v>2982</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="43">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>11.2</v>
+        <v>29</v>
       </c>
       <c r="C43" t="n">
-        <v>2443</v>
+        <v>3904</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44">
@@ -1345,18 +1345,18 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-1.7</v>
+        <v>32.6</v>
       </c>
       <c r="C44" t="n">
-        <v>29</v>
+        <v>3919</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="45">
@@ -1366,18 +1366,18 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="C45" t="n">
-        <v>128</v>
+        <v>1604</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>18.6</v>
+        <v>-3.9</v>
       </c>
       <c r="C46" t="n">
-        <v>3480</v>
+        <v>2946</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="47">
@@ -1408,18 +1408,18 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.3</v>
+        <v>22.7</v>
       </c>
       <c r="C47" t="n">
-        <v>136</v>
+        <v>2370</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48">
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>20.4</v>
+        <v>18.9</v>
       </c>
       <c r="C48" t="n">
-        <v>2057</v>
+        <v>1760</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="49">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C49" t="n">
-        <v>2431</v>
+        <v>3490</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="50">
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>14.8</v>
+        <v>32.9</v>
       </c>
       <c r="C50" t="n">
-        <v>1936</v>
+        <v>1828</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1.5</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="51">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>14.7</v>
+        <v>19.1</v>
       </c>
       <c r="C51" t="n">
-        <v>3984</v>
+        <v>1670</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52">
@@ -1513,18 +1513,18 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-2.2</v>
+        <v>-16.4</v>
       </c>
       <c r="C52" t="n">
-        <v>80</v>
+        <v>3642</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="53">
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>14</v>
+        <v>24.9</v>
       </c>
       <c r="C53" t="n">
-        <v>3232</v>
+        <v>3739</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-15</v>
+        <v>16.8</v>
       </c>
       <c r="C54" t="n">
-        <v>1953</v>
+        <v>2284</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="55">
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>32.8</v>
+        <v>13.6</v>
       </c>
       <c r="C55" t="n">
-        <v>3094</v>
+        <v>1363</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56">
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.9</v>
+        <v>25.8</v>
       </c>
       <c r="C56" t="n">
-        <v>1002</v>
+        <v>1820</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="57">
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7</v>
+        <v>15.2</v>
       </c>
       <c r="C57" t="n">
-        <v>3731</v>
+        <v>3078</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2.5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4.4</v>
+        <v>-2</v>
       </c>
       <c r="C58" t="n">
-        <v>3829</v>
+        <v>3596</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="59">
@@ -1660,10 +1660,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>15.9</v>
+        <v>17.3</v>
       </c>
       <c r="C59" t="n">
-        <v>1947</v>
+        <v>3372</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3.5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="60">
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>16.2</v>
+        <v>34.5</v>
       </c>
       <c r="C60" t="n">
-        <v>3311</v>
+        <v>1983</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="61">
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>9</v>
+        <v>24.9</v>
       </c>
       <c r="C61" t="n">
-        <v>3250</v>
+        <v>2619</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62">
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>22.8</v>
+        <v>-2.6</v>
       </c>
       <c r="C62" t="n">
-        <v>2334</v>
+        <v>3425</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="63">
@@ -1744,18 +1744,18 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-6.1</v>
+        <v>25.7</v>
       </c>
       <c r="C63" t="n">
-        <v>127</v>
+        <v>3860</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>10.3</v>
+        <v>-2.8</v>
       </c>
       <c r="C64" t="n">
-        <v>3719</v>
+        <v>3493</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="65">
@@ -1786,18 +1786,18 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-4.4</v>
+        <v>12.3</v>
       </c>
       <c r="C65" t="n">
-        <v>41</v>
+        <v>2163</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="66">
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-5.5</v>
+        <v>31.5</v>
       </c>
       <c r="C66" t="n">
-        <v>2587</v>
+        <v>2781</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="67">
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>16.4</v>
+        <v>17.1</v>
       </c>
       <c r="C67" t="n">
-        <v>3101</v>
+        <v>2296</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68">
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>13.2</v>
+        <v>11.9</v>
       </c>
       <c r="C68" t="n">
-        <v>3908</v>
+        <v>3037</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1.5</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="69">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>17.2</v>
+        <v>10.6</v>
       </c>
       <c r="C69" t="n">
-        <v>2482</v>
+        <v>3480</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="70">
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>11.6</v>
+        <v>-1.2</v>
       </c>
       <c r="C70" t="n">
-        <v>1954</v>
+        <v>3475</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="71">
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>27.8</v>
+        <v>2.8</v>
       </c>
       <c r="C71" t="n">
-        <v>1427</v>
+        <v>1509</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="72">
@@ -1933,18 +1933,18 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1.5</v>
+        <v>-0.7</v>
       </c>
       <c r="C72" t="n">
-        <v>103</v>
+        <v>2279</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="73">
@@ -1954,18 +1954,18 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-3.6</v>
+        <v>50.3</v>
       </c>
       <c r="C73" t="n">
-        <v>127</v>
+        <v>2057</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="74">
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>16.8</v>
+        <v>7</v>
       </c>
       <c r="C74" t="n">
-        <v>3669</v>
+        <v>1483</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.5</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="75">
@@ -1996,18 +1996,18 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="C75" t="n">
-        <v>67</v>
+        <v>2431</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="76">
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>9.4</v>
+        <v>3.7</v>
       </c>
       <c r="C76" t="n">
-        <v>2100</v>
+        <v>2295</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.5</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="77">
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1.7</v>
+        <v>31.8</v>
       </c>
       <c r="C77" t="n">
-        <v>2018</v>
+        <v>2320</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78">
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>22.6</v>
+        <v>-8</v>
       </c>
       <c r="C78" t="n">
-        <v>3904</v>
+        <v>3289</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1.5</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="79">
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>51.7</v>
+        <v>14.7</v>
       </c>
       <c r="C79" t="n">
-        <v>1845</v>
+        <v>3799</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80">
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>14.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="C80" t="n">
-        <v>2885</v>
+        <v>3952</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2.5</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="81">
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C81" t="n">
-        <v>2874</v>
+        <v>2559</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="82">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>31.4</v>
+        <v>8.1</v>
       </c>
       <c r="C82" t="n">
-        <v>1597</v>
+        <v>3232</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3.5</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="83">
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>29.1</v>
+        <v>9.9</v>
       </c>
       <c r="C83" t="n">
-        <v>3867</v>
+        <v>2507</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
     </row>
     <row r="84">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>32.8</v>
+        <v>28.7</v>
       </c>
       <c r="C84" t="n">
-        <v>1458</v>
+        <v>3577</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4.5</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="85">
@@ -2206,18 +2206,18 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C85" t="n">
-        <v>45</v>
+        <v>922</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="86">
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>22.3</v>
+        <v>5.4</v>
       </c>
       <c r="C86" t="n">
-        <v>2946</v>
+        <v>1200</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.5</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="87">
@@ -2248,10 +2248,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-8.300000000000001</v>
+        <v>31.6</v>
       </c>
       <c r="C87" t="n">
-        <v>1499</v>
+        <v>3731</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="88">
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3.6</v>
+        <v>29.6</v>
       </c>
       <c r="C88" t="n">
-        <v>990</v>
+        <v>997</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1.5</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="89">
@@ -2290,10 +2290,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>7.8</v>
+        <v>10.3</v>
       </c>
       <c r="C89" t="n">
-        <v>927</v>
+        <v>2991</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="90">
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1.2</v>
+        <v>15.3</v>
       </c>
       <c r="C90" t="n">
-        <v>2558</v>
+        <v>1408</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2.5</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="91">
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>31.7</v>
+        <v>0.6</v>
       </c>
       <c r="C91" t="n">
-        <v>3337</v>
+        <v>3311</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="92">
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>20.4</v>
+        <v>35.5</v>
       </c>
       <c r="C92" t="n">
-        <v>1584</v>
+        <v>2594</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3.5</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="93">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>36.3</v>
+        <v>25.5</v>
       </c>
       <c r="C93" t="n">
-        <v>1337</v>
+        <v>3250</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="94">
@@ -2395,18 +2395,18 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>6.2</v>
+        <v>-7.8</v>
       </c>
       <c r="C94" t="n">
-        <v>1720</v>
+        <v>89</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="C95" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2437,18 +2437,18 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>13</v>
+        <v>-0.7</v>
       </c>
       <c r="C96" t="n">
-        <v>3168</v>
+        <v>51</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-3.4</v>
+        <v>3.1</v>
       </c>
       <c r="C97" t="n">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -2479,18 +2479,18 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-3.7</v>
+        <v>2.4</v>
       </c>
       <c r="C98" t="n">
-        <v>1915</v>
+        <v>81</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -2500,18 +2500,18 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>39</v>
+        <v>4.6</v>
       </c>
       <c r="C99" t="n">
-        <v>850</v>
+        <v>41</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -2521,18 +2521,18 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>10</v>
+        <v>-3.1</v>
       </c>
       <c r="C100" t="n">
-        <v>1374</v>
+        <v>98</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>3</v>
+        <v>-2.6</v>
       </c>
       <c r="C101" t="n">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -2563,18 +2563,18 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>26.6</v>
+        <v>0.3</v>
       </c>
       <c r="C102" t="n">
-        <v>3291</v>
+        <v>59</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2584,18 +2584,18 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>8.9</v>
+        <v>2.5</v>
       </c>
       <c r="C103" t="n">
-        <v>804</v>
+        <v>8</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -2605,18 +2605,18 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>15.5</v>
+        <v>4.1</v>
       </c>
       <c r="C104" t="n">
-        <v>1573</v>
+        <v>98</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -2626,18 +2626,18 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
       <c r="C105" t="n">
-        <v>3670</v>
+        <v>147</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2647,10 +2647,10 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.1</v>
+        <v>3.1</v>
       </c>
       <c r="C106" t="n">
-        <v>143</v>
+        <v>53</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -2668,18 +2668,18 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>20.3</v>
+        <v>6.1</v>
       </c>
       <c r="C107" t="n">
-        <v>1456</v>
+        <v>74</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2689,18 +2689,18 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="C108" t="n">
-        <v>2610</v>
+        <v>112</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-0.6</v>
+        <v>-3.6</v>
       </c>
       <c r="C109" t="n">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -2731,18 +2731,18 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-3.9</v>
+        <v>17.1</v>
       </c>
       <c r="C110" t="n">
-        <v>126</v>
+        <v>3761</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="111">
@@ -2752,18 +2752,18 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>8.300000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>3669</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>36.2</v>
+        <v>0.7</v>
       </c>
       <c r="C112" t="n">
-        <v>1919</v>
+        <v>4034</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="113">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>19.9</v>
+        <v>22.9</v>
       </c>
       <c r="C113" t="n">
-        <v>1696</v>
+        <v>960</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>40.5</v>
+        <v>6</v>
       </c>
       <c r="C114" t="n">
-        <v>1503</v>
+        <v>2403</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="115">
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>27.4</v>
+        <v>1.4</v>
       </c>
       <c r="C115" t="n">
-        <v>3947</v>
+        <v>2327</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>10.9</v>
+        <v>25.4</v>
       </c>
       <c r="C116" t="n">
-        <v>1796</v>
+        <v>2719</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="117">
@@ -2878,18 +2878,18 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-4.1</v>
+        <v>26.5</v>
       </c>
       <c r="C117" t="n">
-        <v>46</v>
+        <v>1439</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118">
@@ -2899,18 +2899,18 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-0.1</v>
+        <v>22.6</v>
       </c>
       <c r="C118" t="n">
-        <v>143</v>
+        <v>3904</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="119">
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>3.8</v>
+        <v>51.7</v>
       </c>
       <c r="C119" t="n">
-        <v>2112</v>
+        <v>1269</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120">
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>34.6</v>
+        <v>25.5</v>
       </c>
       <c r="C120" t="n">
-        <v>1156</v>
+        <v>1845</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="121">
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-2.2</v>
+        <v>12.1</v>
       </c>
       <c r="C121" t="n">
-        <v>3649</v>
+        <v>2874</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122">
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>15</v>
+        <v>30.6</v>
       </c>
       <c r="C122" t="n">
-        <v>3609</v>
+        <v>1025</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="123">
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>24.1</v>
+        <v>-1.1</v>
       </c>
       <c r="C123" t="n">
-        <v>1315</v>
+        <v>3726</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124">
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>12.6</v>
+        <v>10.5</v>
       </c>
       <c r="C124" t="n">
-        <v>1135</v>
+        <v>1759</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="125">
@@ -3046,10 +3046,10 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>15.7</v>
+        <v>21</v>
       </c>
       <c r="C125" t="n">
-        <v>1651</v>
+        <v>1615</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126">
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>2.6</v>
+        <v>32.8</v>
       </c>
       <c r="C126" t="n">
-        <v>3537</v>
+        <v>1458</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="127">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>17.5</v>
+        <v>19.8</v>
       </c>
       <c r="C127" t="n">
-        <v>2436</v>
+        <v>816</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="128">
@@ -3109,10 +3109,10 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1.3</v>
+        <v>12.3</v>
       </c>
       <c r="C128" t="n">
-        <v>2240</v>
+        <v>4043</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="129">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>22.1</v>
+        <v>23.6</v>
       </c>
       <c r="C129" t="n">
-        <v>811</v>
+        <v>2568</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="130">
@@ -3151,18 +3151,18 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.6</v>
+        <v>13.5</v>
       </c>
       <c r="C130" t="n">
-        <v>129</v>
+        <v>1860</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="131">
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>9.800000000000001</v>
+        <v>23.9</v>
       </c>
       <c r="C131" t="n">
-        <v>889</v>
+        <v>980</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="132">
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="C132" t="n">
-        <v>3817</v>
+        <v>1406</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="133">
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>10.7</v>
+        <v>-3.2</v>
       </c>
       <c r="C133" t="n">
-        <v>2316</v>
+        <v>2806</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="134">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>7.4</v>
+        <v>3.9</v>
       </c>
       <c r="C134" t="n">
-        <v>1528</v>
+        <v>1984</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="135">
@@ -3256,18 +3256,18 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>4.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="C135" t="n">
-        <v>98</v>
+        <v>2616</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="136">
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>20.9</v>
+        <v>1.2</v>
       </c>
       <c r="C136" t="n">
-        <v>1777</v>
+        <v>2558</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="137">
@@ -3298,10 +3298,10 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-3.3</v>
+        <v>31.7</v>
       </c>
       <c r="C137" t="n">
-        <v>836</v>
+        <v>954</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="138">
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>4.6</v>
+        <v>19.3</v>
       </c>
       <c r="C138" t="n">
-        <v>2348</v>
+        <v>3337</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="139">
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>24.5</v>
+        <v>21.7</v>
       </c>
       <c r="C139" t="n">
-        <v>2909</v>
+        <v>1045</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="140">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>23.2</v>
+        <v>-6.6</v>
       </c>
       <c r="C140" t="n">
-        <v>1528</v>
+        <v>4047</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="141">
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>11.3</v>
+        <v>20.6</v>
       </c>
       <c r="C141" t="n">
-        <v>1195</v>
+        <v>1337</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="142">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>19.7</v>
+        <v>22.9</v>
       </c>
       <c r="C142" t="n">
-        <v>875</v>
+        <v>2690</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="143">
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>13.5</v>
+        <v>-2.2</v>
       </c>
       <c r="C143" t="n">
-        <v>1650</v>
+        <v>3675</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="144">
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-6.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C144" t="n">
-        <v>943</v>
+        <v>2329</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="145">
@@ -3466,10 +3466,10 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="C145" t="n">
-        <v>3738</v>
+        <v>2706</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="146">
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>10.9</v>
+        <v>15.8</v>
       </c>
       <c r="C146" t="n">
-        <v>4022</v>
+        <v>3318</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="147">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>18</v>
+        <v>10.1</v>
       </c>
       <c r="C147" t="n">
-        <v>2009</v>
+        <v>2623</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148">
@@ -3529,18 +3529,18 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="C148" t="n">
-        <v>121</v>
+        <v>3574</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="149">
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>13.2</v>
+        <v>29.4</v>
       </c>
       <c r="C149" t="n">
-        <v>3505</v>
+        <v>1374</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150">
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>22.4</v>
+        <v>23.2</v>
       </c>
       <c r="C150" t="n">
-        <v>3880</v>
+        <v>4061</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="151">
@@ -3592,18 +3592,18 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>6.8</v>
+        <v>-4.4</v>
       </c>
       <c r="C151" t="n">
-        <v>6</v>
+        <v>3152</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="152">
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>9.300000000000001</v>
+        <v>-8.9</v>
       </c>
       <c r="C152" t="n">
-        <v>1991</v>
+        <v>2515</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="153">
@@ -3634,18 +3634,18 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1.2</v>
+        <v>20.1</v>
       </c>
       <c r="C153" t="n">
-        <v>82</v>
+        <v>3111</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="154">
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>28.9</v>
+        <v>29.5</v>
       </c>
       <c r="C154" t="n">
-        <v>2188</v>
+        <v>3924</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.5</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="155">
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>9.300000000000001</v>
+        <v>13.2</v>
       </c>
       <c r="C155" t="n">
-        <v>1016</v>
+        <v>1791</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="156">
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>6.4</v>
+        <v>35</v>
       </c>
       <c r="C156" t="n">
-        <v>2627</v>
+        <v>3731</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="157">
@@ -3718,10 +3718,10 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>12.4</v>
+        <v>6.1</v>
       </c>
       <c r="C157" t="n">
-        <v>2005</v>
+        <v>3783</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="158">
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>11.4</v>
+        <v>15.2</v>
       </c>
       <c r="C158" t="n">
-        <v>1513</v>
+        <v>3503</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2.5</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="159">
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>14.9</v>
+        <v>20.3</v>
       </c>
       <c r="C159" t="n">
-        <v>1881</v>
+        <v>2493</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="160">
@@ -3781,10 +3781,10 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>18.9</v>
+        <v>7.1</v>
       </c>
       <c r="C160" t="n">
-        <v>1255</v>
+        <v>2482</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>3.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="161">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>5.1</v>
+        <v>25.2</v>
       </c>
       <c r="C161" t="n">
-        <v>2796</v>
+        <v>1881</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="162">
@@ -3823,10 +3823,10 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-2.3</v>
+        <v>6.2</v>
       </c>
       <c r="C162" t="n">
-        <v>1304</v>
+        <v>2774</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>4.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="163">
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>4.9</v>
+        <v>8.1</v>
       </c>
       <c r="C163" t="n">
-        <v>1733</v>
+        <v>2653</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="164">
@@ -3865,10 +3865,10 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>17.7</v>
+        <v>36.4</v>
       </c>
       <c r="C164" t="n">
-        <v>2905</v>
+        <v>3638</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="165">
@@ -3886,18 +3886,18 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.1</v>
+        <v>6.9</v>
       </c>
       <c r="C165" t="n">
-        <v>146</v>
+        <v>2464</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="166">
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>32.4</v>
+        <v>13.6</v>
       </c>
       <c r="C166" t="n">
-        <v>2894</v>
+        <v>1881</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.5</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="167">
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>26.5</v>
+        <v>25</v>
       </c>
       <c r="C167" t="n">
-        <v>2196</v>
+        <v>1919</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="168">
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>19.4</v>
+        <v>26.3</v>
       </c>
       <c r="C168" t="n">
-        <v>3503</v>
+        <v>1941</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1.5</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="169">
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>17.5</v>
+        <v>30.2</v>
       </c>
       <c r="C169" t="n">
-        <v>3631</v>
+        <v>1696</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="170">
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>11.3</v>
+        <v>19.5</v>
       </c>
       <c r="C170" t="n">
-        <v>3819</v>
+        <v>2012</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2.5</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="171">
@@ -4012,18 +4012,18 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-3.7</v>
+        <v>34.8</v>
       </c>
       <c r="C171" t="n">
-        <v>89</v>
+        <v>3637</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="172">
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>5.4</v>
+        <v>-3.2</v>
       </c>
       <c r="C172" t="n">
-        <v>4049</v>
+        <v>3708</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="173">
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-1.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C173" t="n">
-        <v>2746</v>
+        <v>2479</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="174">
@@ -4075,10 +4075,10 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>7.3</v>
+        <v>10.9</v>
       </c>
       <c r="C174" t="n">
-        <v>4016</v>
+        <v>1796</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="175">
@@ -4096,10 +4096,10 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-4.2</v>
+        <v>5.2</v>
       </c>
       <c r="C175" t="n">
-        <v>3599</v>
+        <v>2043</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="176">
@@ -4117,18 +4117,18 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>8.4</v>
+        <v>11.6</v>
       </c>
       <c r="C176" t="n">
-        <v>45</v>
+        <v>1892</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>0</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="177">
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>-5.8</v>
+        <v>7.8</v>
       </c>
       <c r="C177" t="n">
-        <v>809</v>
+        <v>1757</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>0.5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="178">
@@ -4159,10 +4159,10 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>11.3</v>
+        <v>23.4</v>
       </c>
       <c r="C178" t="n">
-        <v>1676</v>
+        <v>3859</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="179">
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>1</v>
+        <v>22.2</v>
       </c>
       <c r="C179" t="n">
-        <v>2993</v>
+        <v>2435</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="180">
@@ -4201,10 +4201,10 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>31.5</v>
+        <v>40.4</v>
       </c>
       <c r="C180" t="n">
-        <v>3024</v>
+        <v>2112</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>2</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="181">
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>6.9</v>
+        <v>9</v>
       </c>
       <c r="C181" t="n">
-        <v>3674</v>
+        <v>2585</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>2.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="182">
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>17.6</v>
+        <v>15</v>
       </c>
       <c r="C182" t="n">
-        <v>2284</v>
+        <v>3369</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>3</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="183">
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>9.199999999999999</v>
+        <v>24.1</v>
       </c>
       <c r="C183" t="n">
-        <v>2468</v>
+        <v>1815</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>3.5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="184">
@@ -4285,10 +4285,10 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>34.2</v>
+        <v>26.7</v>
       </c>
       <c r="C184" t="n">
-        <v>2260</v>
+        <v>2148</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>4</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="185">
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>22.2</v>
+        <v>33.5</v>
       </c>
       <c r="C185" t="n">
-        <v>882</v>
+        <v>1135</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>4.5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="186">
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>7.1</v>
+        <v>29.1</v>
       </c>
       <c r="C186" t="n">
-        <v>3949</v>
+        <v>2582</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>5</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="187">
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>5.7</v>
+        <v>21.4</v>
       </c>
       <c r="C187" t="n">
-        <v>2269</v>
+        <v>2731</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5.5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="188">
@@ -4369,10 +4369,10 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>-3.4</v>
+        <v>2.6</v>
       </c>
       <c r="C188" t="n">
-        <v>1287</v>
+        <v>3537</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="189">
@@ -4390,18 +4390,18 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="C189" t="n">
-        <v>117</v>
+        <v>1756</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="190">
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>8.199999999999999</v>
+        <v>20.4</v>
       </c>
       <c r="C190" t="n">
-        <v>1067</v>
+        <v>3538</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>0.5</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="191">
@@ -4432,10 +4432,10 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>45.5</v>
+        <v>28.6</v>
       </c>
       <c r="C191" t="n">
-        <v>2052</v>
+        <v>2240</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="192">
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>17.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C192" t="n">
-        <v>1377</v>
+        <v>1991</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1.5</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="193">
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>15.6</v>
+        <v>17.5</v>
       </c>
       <c r="C193" t="n">
-        <v>3645</v>
+        <v>1575</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="194">
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>11.8</v>
+        <v>7.9</v>
       </c>
       <c r="C194" t="n">
-        <v>3282</v>
+        <v>3452</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>2.5</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="195">
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>23.6</v>
+        <v>25.2</v>
       </c>
       <c r="C195" t="n">
-        <v>3831</v>
+        <v>4067</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="196">
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>26.8</v>
+        <v>26.4</v>
       </c>
       <c r="C196" t="n">
-        <v>1341</v>
+        <v>1625</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>3.5</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="197">
@@ -4558,10 +4558,10 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>19</v>
+        <v>32.4</v>
       </c>
       <c r="C197" t="n">
-        <v>3747</v>
+        <v>1212</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="198">
@@ -4579,10 +4579,10 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>16.5</v>
+        <v>7.4</v>
       </c>
       <c r="C198" t="n">
-        <v>2153</v>
+        <v>1528</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>4.5</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="199">
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>9.199999999999999</v>
+        <v>25.5</v>
       </c>
       <c r="C199" t="n">
-        <v>2973</v>
+        <v>2692</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="200">
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>-11.1</v>
+        <v>37.4</v>
       </c>
       <c r="C200" t="n">
-        <v>2706</v>
+        <v>3304</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>5.5</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="201">
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>39.4</v>
+        <v>35.3</v>
       </c>
       <c r="C201" t="n">
-        <v>2794</v>
+        <v>1922</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
     </row>
     <row r="202">
@@ -4663,18 +4663,18 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>2.8</v>
+        <v>30.3</v>
       </c>
       <c r="C202" t="n">
-        <v>7</v>
+        <v>2371</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>0</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="203">
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>4.1</v>
+        <v>7.9</v>
       </c>
       <c r="C203" t="n">
-        <v>2687</v>
+        <v>2487</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>0.5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="204">
@@ -4705,10 +4705,10 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>15.9</v>
+        <v>33.6</v>
       </c>
       <c r="C204" t="n">
-        <v>892</v>
+        <v>3510</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="205">
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>19.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="C205" t="n">
-        <v>1828</v>
+        <v>3064</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1.5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="206">
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>13.7</v>
+        <v>30.7</v>
       </c>
       <c r="C206" t="n">
-        <v>1481</v>
+        <v>3714</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>2</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="207">
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>2.6</v>
+        <v>15.3</v>
       </c>
       <c r="C207" t="n">
-        <v>3393</v>
+        <v>2165</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>2.5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="208">
@@ -4789,18 +4789,18 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>-3.1</v>
+        <v>12.1</v>
       </c>
       <c r="C208" t="n">
-        <v>44</v>
+        <v>1196</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>0</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="209">
@@ -4810,10 +4810,10 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>11.7</v>
+        <v>25.2</v>
       </c>
       <c r="C209" t="n">
-        <v>3061</v>
+        <v>1195</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>0.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="210">
@@ -4831,18 +4831,18 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>-1.9</v>
+        <v>18.9</v>
       </c>
       <c r="C210" t="n">
-        <v>93</v>
+        <v>3292</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>0</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="211">
@@ -4852,18 +4852,18 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>-5.3</v>
+        <v>13.4</v>
       </c>
       <c r="C211" t="n">
-        <v>35</v>
+        <v>1650</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="212">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>17.1</v>
+        <v>28.5</v>
       </c>
       <c r="C212" t="n">
-        <v>1424</v>
+        <v>2190</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>0.5</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="213">
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>15.4</v>
+        <v>40.7</v>
       </c>
       <c r="C213" t="n">
-        <v>855</v>
+        <v>2292</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="214">
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>17.3</v>
+        <v>10.9</v>
       </c>
       <c r="C214" t="n">
-        <v>1273</v>
+        <v>4022</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1.5</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="215">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>34.2</v>
+        <v>18</v>
       </c>
       <c r="C215" t="n">
-        <v>3513</v>
+        <v>1865</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="216">
@@ -4957,18 +4957,18 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>2</v>
+        <v>15.9</v>
       </c>
       <c r="C216" t="n">
-        <v>55</v>
+        <v>2009</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>0</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="217">
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="C217" t="n">
-        <v>3210</v>
+        <v>1956</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>0.5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="218">
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>-4.3</v>
+        <v>11.3</v>
       </c>
       <c r="C218" t="n">
-        <v>3653</v>
+        <v>4034</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="219">
@@ -5020,10 +5020,10 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>17.4</v>
+        <v>24.6</v>
       </c>
       <c r="C219" t="n">
-        <v>1284</v>
+        <v>3505</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1.5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="220">
@@ -5041,18 +5041,18 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>-5.3</v>
+        <v>20</v>
       </c>
       <c r="C220" t="n">
-        <v>38</v>
+        <v>1550</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>0</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="221">
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C221" t="n">
-        <v>3659</v>
+        <v>3339</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>0.5</v>
+        <v>56</v>
       </c>
     </row>
     <row r="222">
@@ -5083,10 +5083,10 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>-11.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C222" t="n">
-        <v>4083</v>
+        <v>3760</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="223">
@@ -5104,10 +5104,10 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>10.3</v>
+        <v>17.4</v>
       </c>
       <c r="C223" t="n">
-        <v>1969</v>
+        <v>3793</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1.5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="224">
@@ -5125,18 +5125,18 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C224" t="n">
-        <v>110</v>
+        <v>3642</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>0</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="225">
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>34.8</v>
+        <v>17.8</v>
       </c>
       <c r="C225" t="n">
-        <v>3595</v>
+        <v>4036</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>0.5</v>
+        <v>58</v>
       </c>
     </row>
     <row r="226">
@@ -5167,18 +5167,18 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>7</v>
+        <v>28.9</v>
       </c>
       <c r="C226" t="n">
-        <v>100</v>
+        <v>2245</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>0</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="227">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>-0.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C227" t="n">
-        <v>2775</v>
+        <v>1310</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>0.5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="228">
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>-1.8</v>
+        <v>-5.9</v>
       </c>
       <c r="C228" t="n">
-        <v>2789</v>
+        <v>1016</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="229">
@@ -5230,18 +5230,18 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>2.8</v>
+        <v>27.8</v>
       </c>
       <c r="C229" t="n">
-        <v>69</v>
+        <v>2610</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="230">
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>24.6</v>
+        <v>32.7</v>
       </c>
       <c r="C230" t="n">
-        <v>3363</v>
+        <v>3292</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>0.5</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="231">
@@ -5272,18 +5272,18 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="C231" t="n">
-        <v>117</v>
+        <v>1513</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="232">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>24.8</v>
+        <v>6.3</v>
       </c>
       <c r="C232" t="n">
-        <v>3351</v>
+        <v>2681</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>0.5</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="233">
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>21.8</v>
+        <v>-7.5</v>
       </c>
       <c r="C233" t="n">
-        <v>3562</v>
+        <v>972</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
     </row>
     <row r="234">
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>9.800000000000001</v>
+        <v>32.3</v>
       </c>
       <c r="C234" t="n">
-        <v>2258</v>
+        <v>1452</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>1.5</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="235">
@@ -5356,10 +5356,10 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>20.9</v>
+        <v>-8</v>
       </c>
       <c r="C235" t="n">
-        <v>3683</v>
+        <v>2483</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
     </row>
     <row r="236">
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>17.6</v>
+        <v>22.8</v>
       </c>
       <c r="C236" t="n">
-        <v>1024</v>
+        <v>3323</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>2.5</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="237">
@@ -5398,10 +5398,10 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>35.5</v>
+        <v>21.4</v>
       </c>
       <c r="C237" t="n">
-        <v>1453</v>
+        <v>2758</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
     </row>
     <row r="238">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>24.2</v>
+        <v>1.7</v>
       </c>
       <c r="C238" t="n">
-        <v>2628</v>
+        <v>3872</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>3.5</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="239">
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>15.1</v>
+        <v>24.1</v>
       </c>
       <c r="C239" t="n">
-        <v>3106</v>
+        <v>1304</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>4</v>
+        <v>65</v>
       </c>
     </row>
     <row r="240">
@@ -5461,18 +5461,18 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="C240" t="n">
-        <v>9</v>
+        <v>2014</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>0</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="241">
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>38.8</v>
+        <v>14.5</v>
       </c>
       <c r="C241" t="n">
-        <v>1991</v>
+        <v>1728</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>0.5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="242">
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>14.1</v>
+        <v>31.3</v>
       </c>
       <c r="C242" t="n">
-        <v>1120</v>
+        <v>1733</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="243">
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>2.7</v>
+        <v>11.6</v>
       </c>
       <c r="C243" t="n">
-        <v>1918</v>
+        <v>1484</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>1.5</v>
+        <v>67</v>
       </c>
     </row>
     <row r="244">
@@ -5545,10 +5545,10 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>8.300000000000001</v>
+        <v>-7.8</v>
       </c>
       <c r="C244" t="n">
-        <v>3165</v>
+        <v>3519</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>2</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="245">
@@ -5566,10 +5566,10 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>33.1</v>
+        <v>22.2</v>
       </c>
       <c r="C245" t="n">
-        <v>1960</v>
+        <v>879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>2.5</v>
+        <v>68</v>
       </c>
     </row>
     <row r="246">
@@ -5587,18 +5587,18 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>17.2</v>
+        <v>4.2</v>
       </c>
       <c r="C246" t="n">
-        <v>2370</v>
+        <v>117</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -5608,10 +5608,10 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>1.8</v>
+        <v>-5.3</v>
       </c>
       <c r="C247" t="n">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -5629,10 +5629,10 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>3.8</v>
+        <v>7.3</v>
       </c>
       <c r="C248" t="n">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -5650,18 +5650,18 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>22.7</v>
+        <v>4.8</v>
       </c>
       <c r="C249" t="n">
-        <v>4036</v>
+        <v>0</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -5671,18 +5671,18 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>-11.5</v>
+        <v>-4.5</v>
       </c>
       <c r="C250" t="n">
-        <v>877</v>
+        <v>116</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -5692,18 +5692,18 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>19.3</v>
+        <v>7.6</v>
       </c>
       <c r="C251" t="n">
-        <v>2936</v>
+        <v>11</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -5713,18 +5713,18 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>-9.5</v>
+        <v>10.9</v>
       </c>
       <c r="C252" t="n">
-        <v>2663</v>
+        <v>73</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -5734,18 +5734,18 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>2.9</v>
+        <v>-4</v>
       </c>
       <c r="C253" t="n">
-        <v>3269</v>
+        <v>7</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -5755,18 +5755,18 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>-4</v>
+        <v>-0.8</v>
       </c>
       <c r="C254" t="n">
-        <v>1374</v>
+        <v>121</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -5776,18 +5776,18 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>15.2</v>
+        <v>-6.8</v>
       </c>
       <c r="C255" t="n">
-        <v>1302</v>
+        <v>59</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -5797,18 +5797,18 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>17.8</v>
+        <v>-9.6</v>
       </c>
       <c r="C256" t="n">
-        <v>1620</v>
+        <v>27</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -5818,10 +5818,10 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="C257" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -5839,18 +5839,18 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="C258" t="n">
-        <v>2002</v>
+        <v>45</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -5860,18 +5860,18 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>10.2</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="C259" t="n">
-        <v>2492</v>
+        <v>9</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -5881,18 +5881,18 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>17.2</v>
+        <v>0.7</v>
       </c>
       <c r="C260" t="n">
-        <v>1277</v>
+        <v>55</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -5902,10 +5902,10 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="C261" t="n">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -5923,18 +5923,18 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>10.8</v>
+        <v>7</v>
       </c>
       <c r="C262" t="n">
-        <v>1750</v>
+        <v>118</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -5944,18 +5944,18 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>9.9</v>
+        <v>-2.2</v>
       </c>
       <c r="C263" t="n">
-        <v>1316</v>
+        <v>145</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -5965,18 +5965,18 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>16</v>
+        <v>-8.6</v>
       </c>
       <c r="C264" t="n">
-        <v>3712</v>
+        <v>10</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -5986,18 +5986,18 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>3.6</v>
+        <v>6.8</v>
       </c>
       <c r="C265" t="n">
-        <v>2700</v>
+        <v>85</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -6007,10 +6007,10 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>-2.2</v>
+        <v>1.4</v>
       </c>
       <c r="C266" t="n">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -6028,18 +6028,18 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>19.5</v>
+        <v>1.4</v>
       </c>
       <c r="C267" t="n">
-        <v>3691</v>
+        <v>97</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -6049,18 +6049,18 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>31</v>
+        <v>-8</v>
       </c>
       <c r="C268" t="n">
-        <v>894</v>
+        <v>104</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
@@ -6070,18 +6070,18 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>39</v>
+        <v>-3</v>
       </c>
       <c r="C269" t="n">
-        <v>2916</v>
+        <v>54</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -6091,18 +6091,18 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="C270" t="n">
-        <v>2665</v>
+        <v>5</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -6112,18 +6112,18 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="C271" t="n">
-        <v>1145</v>
+        <v>132</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -6133,18 +6133,18 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>11.8</v>
+        <v>0.8</v>
       </c>
       <c r="C272" t="n">
-        <v>3243</v>
+        <v>101</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -6154,18 +6154,18 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>9.699999999999999</v>
+        <v>4</v>
       </c>
       <c r="C273" t="n">
-        <v>3530</v>
+        <v>52</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -6175,18 +6175,18 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>7.8</v>
+        <v>-1.6</v>
       </c>
       <c r="C274" t="n">
-        <v>1155</v>
+        <v>82</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -6196,10 +6196,10 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>6.5</v>
+        <v>-8</v>
       </c>
       <c r="C275" t="n">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -6217,10 +6217,10 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>3.1</v>
+        <v>16.4</v>
       </c>
       <c r="C276" t="n">
-        <v>3626</v>
+        <v>2848</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>13.5</v>
+        <v>21.2</v>
       </c>
       <c r="C277" t="n">
-        <v>2445</v>
+        <v>2269</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -6259,18 +6259,18 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>-6.2</v>
+        <v>27.7</v>
       </c>
       <c r="C278" t="n">
-        <v>56</v>
+        <v>1248</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="279">
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>1.8</v>
+        <v>33.5</v>
       </c>
       <c r="C279" t="n">
-        <v>2734</v>
+        <v>2942</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280">
@@ -6301,10 +6301,10 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>5.4</v>
+        <v>15</v>
       </c>
       <c r="C280" t="n">
-        <v>3816</v>
+        <v>3943</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="281">
@@ -6322,10 +6322,10 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>22.9</v>
+        <v>9.9</v>
       </c>
       <c r="C281" t="n">
-        <v>1736</v>
+        <v>1237</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
@@ -6343,18 +6343,18 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>-7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="C282" t="n">
-        <v>24</v>
+        <v>2965</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="283">
@@ -6364,10 +6364,10 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>-18.4</v>
+        <v>25.7</v>
       </c>
       <c r="C283" t="n">
-        <v>3487</v>
+        <v>2784</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="284">
@@ -6385,10 +6385,10 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>12.7</v>
+        <v>20</v>
       </c>
       <c r="C284" t="n">
-        <v>1675</v>
+        <v>1877</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="285">
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>18.8</v>
+        <v>31.1</v>
       </c>
       <c r="C285" t="n">
-        <v>2003</v>
+        <v>3614</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="286">
@@ -6427,10 +6427,10 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>27.5</v>
+        <v>22.7</v>
       </c>
       <c r="C286" t="n">
-        <v>2679</v>
+        <v>3766</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="287">
@@ -6448,10 +6448,10 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>6.6</v>
+        <v>31.4</v>
       </c>
       <c r="C287" t="n">
-        <v>3513</v>
+        <v>1377</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="288">
@@ -6469,18 +6469,18 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>-1.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C288" t="n">
-        <v>48</v>
+        <v>2922</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="289">
@@ -6490,18 +6490,18 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>-5.5</v>
+        <v>10.9</v>
       </c>
       <c r="C289" t="n">
-        <v>103</v>
+        <v>1563</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="290">
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>4.5</v>
+        <v>27.7</v>
       </c>
       <c r="C290" t="n">
-        <v>2592</v>
+        <v>3585</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="291">
@@ -6532,10 +6532,10 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>-4.3</v>
+        <v>-6.1</v>
       </c>
       <c r="C291" t="n">
-        <v>1751</v>
+        <v>3645</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="292">
@@ -6553,10 +6553,10 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>42.1</v>
+        <v>25.6</v>
       </c>
       <c r="C292" t="n">
-        <v>2879</v>
+        <v>2158</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="293">
@@ -6574,10 +6574,10 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>8.1</v>
+        <v>13.4</v>
       </c>
       <c r="C293" t="n">
-        <v>4015</v>
+        <v>2131</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="294">
@@ -6595,10 +6595,10 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>27.5</v>
+        <v>33</v>
       </c>
       <c r="C294" t="n">
-        <v>2865</v>
+        <v>1048</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="295">
@@ -6616,10 +6616,10 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>3</v>
+        <v>15.9</v>
       </c>
       <c r="C295" t="n">
-        <v>3349</v>
+        <v>1819</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="296">
@@ -6637,10 +6637,10 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>34.1</v>
+        <v>26.8</v>
       </c>
       <c r="C296" t="n">
-        <v>2961</v>
+        <v>1341</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>3.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="297">
@@ -6658,18 +6658,18 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>-0.1</v>
+        <v>19</v>
       </c>
       <c r="C297" t="n">
-        <v>7</v>
+        <v>2980</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="298">
@@ -6679,10 +6679,10 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>21.2</v>
+        <v>-5.4</v>
       </c>
       <c r="C298" t="n">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>0.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="299">
@@ -6700,10 +6700,10 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>11.5</v>
+        <v>14.3</v>
       </c>
       <c r="C299" t="n">
-        <v>2934</v>
+        <v>3831</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="300">
@@ -6721,10 +6721,10 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>26.2</v>
+        <v>14.9</v>
       </c>
       <c r="C300" t="n">
-        <v>2623</v>
+        <v>868</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>1.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="301">
@@ -6742,18 +6742,18 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>6.4</v>
+        <v>19.8</v>
       </c>
       <c r="C301" t="n">
-        <v>66</v>
+        <v>1004</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="302">
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>45.9</v>
+        <v>-0.7</v>
       </c>
       <c r="C302" t="n">
-        <v>3290</v>
+        <v>2973</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>0.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="303">
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>16.8</v>
+        <v>23</v>
       </c>
       <c r="C303" t="n">
-        <v>3426</v>
+        <v>2706</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="304">
@@ -6805,10 +6805,10 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>25.3</v>
+        <v>1.8</v>
       </c>
       <c r="C304" t="n">
-        <v>3854</v>
+        <v>2958</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>1.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="305">
@@ -6826,10 +6826,10 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>22.5</v>
+        <v>20.9</v>
       </c>
       <c r="C305" t="n">
-        <v>2111</v>
+        <v>2519</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="306">
@@ -6847,10 +6847,10 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>11.7</v>
+        <v>14.2</v>
       </c>
       <c r="C306" t="n">
-        <v>3338</v>
+        <v>1080</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>2.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="307">
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>2.3</v>
+        <v>26.5</v>
       </c>
       <c r="C307" t="n">
-        <v>2801</v>
+        <v>892</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="308">
@@ -6889,18 +6889,18 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>3.4</v>
+        <v>9.6</v>
       </c>
       <c r="C308" t="n">
-        <v>6</v>
+        <v>1471</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="309">
@@ -6910,18 +6910,18 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>2.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C309" t="n">
-        <v>146</v>
+        <v>1828</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="310">
@@ -6931,10 +6931,10 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>21.3</v>
+        <v>5.2</v>
       </c>
       <c r="C310" t="n">
-        <v>3547</v>
+        <v>2289</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>0.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="311">
@@ -6952,10 +6952,10 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>18.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C311" t="n">
-        <v>1545</v>
+        <v>2228</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="312">
@@ -6973,10 +6973,10 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>-3.7</v>
+        <v>13.7</v>
       </c>
       <c r="C312" t="n">
-        <v>1506</v>
+        <v>3685</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>1.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="313">
@@ -6994,10 +6994,10 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>22.3</v>
+        <v>2.6</v>
       </c>
       <c r="C313" t="n">
-        <v>1733</v>
+        <v>3193</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="314">
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>-6</v>
+        <v>15.7</v>
       </c>
       <c r="C314" t="n">
-        <v>1704</v>
+        <v>3917</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>2.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="315">
@@ -7036,10 +7036,10 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>8.5</v>
+        <v>-12.4</v>
       </c>
       <c r="C315" t="n">
-        <v>3701</v>
+        <v>2636</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="316">
@@ -7060,7 +7060,7 @@
         <v>14.5</v>
       </c>
       <c r="C316" t="n">
-        <v>1392</v>
+        <v>3944</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>3.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="317">
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>28.2</v>
+        <v>4.2</v>
       </c>
       <c r="C317" t="n">
-        <v>927</v>
+        <v>3061</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="318">
@@ -7099,18 +7099,18 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>10.8</v>
+        <v>0.3</v>
       </c>
       <c r="C318" t="n">
-        <v>113</v>
+        <v>3086</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="319">
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>23.1</v>
+        <v>15.5</v>
       </c>
       <c r="C319" t="n">
-        <v>2581</v>
+        <v>847</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>0.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="320">
@@ -7141,10 +7141,10 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>15.2</v>
+        <v>25.2</v>
       </c>
       <c r="C320" t="n">
-        <v>3341</v>
+        <v>1136</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>1</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="321">
@@ -7162,18 +7162,18 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="C321" t="n">
-        <v>36</v>
+        <v>1424</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="322">
@@ -7183,18 +7183,18 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>6.7</v>
+        <v>8.6</v>
       </c>
       <c r="C322" t="n">
-        <v>145</v>
+        <v>2690</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="323">
@@ -7204,10 +7204,10 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>16.5</v>
+        <v>8.1</v>
       </c>
       <c r="C323" t="n">
-        <v>2881</v>
+        <v>1438</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>0.5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="324">
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>36.7</v>
+        <v>43.5</v>
       </c>
       <c r="C324" t="n">
-        <v>4024</v>
+        <v>855</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>1</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="325">
@@ -7246,18 +7246,18 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>-0.1</v>
+        <v>11.3</v>
       </c>
       <c r="C325" t="n">
-        <v>85</v>
+        <v>2925</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="326">
@@ -7267,18 +7267,18 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="C326" t="n">
-        <v>56</v>
+        <v>4087</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>0</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="327">
@@ -7288,10 +7288,10 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>4</v>
+        <v>16.5</v>
       </c>
       <c r="C327" t="n">
-        <v>2572</v>
+        <v>3546</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>0.5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="328">
@@ -7309,10 +7309,10 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>29.2</v>
+        <v>19.8</v>
       </c>
       <c r="C328" t="n">
-        <v>1254</v>
+        <v>2135</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>1</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="329">
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>18.1</v>
+        <v>5.6</v>
       </c>
       <c r="C329" t="n">
-        <v>1501</v>
+        <v>1718</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>1.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="330">
@@ -7351,10 +7351,10 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>19.5</v>
+        <v>10.7</v>
       </c>
       <c r="C330" t="n">
-        <v>2399</v>
+        <v>3597</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>2</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="331">
@@ -7372,18 +7372,18 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>-0.6</v>
+        <v>25.8</v>
       </c>
       <c r="C331" t="n">
-        <v>35</v>
+        <v>2706</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="332">
@@ -7393,10 +7393,10 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>-3.3</v>
+        <v>18.5</v>
       </c>
       <c r="C332" t="n">
-        <v>828</v>
+        <v>3886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>0.5</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="333">
@@ -7414,10 +7414,10 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>5.4</v>
+        <v>9.1</v>
       </c>
       <c r="C333" t="n">
-        <v>1936</v>
+        <v>2875</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="334">
@@ -7435,10 +7435,10 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>3.6</v>
+        <v>29.3</v>
       </c>
       <c r="C334" t="n">
-        <v>3591</v>
+        <v>1513</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>1.5</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="335">
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>46.6</v>
+        <v>17.7</v>
       </c>
       <c r="C335" t="n">
-        <v>1557</v>
+        <v>2933</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="336">
@@ -7477,18 +7477,18 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>3</v>
+        <v>35.2</v>
       </c>
       <c r="C336" t="n">
-        <v>55</v>
+        <v>925</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>0</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="337">
@@ -7498,18 +7498,18 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>-7.6</v>
+        <v>25.6</v>
       </c>
       <c r="C337" t="n">
-        <v>108</v>
+        <v>866</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="338">
@@ -7519,18 +7519,18 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="C338" t="n">
-        <v>72</v>
+        <v>1032</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>0</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="339">
@@ -7540,10 +7540,10 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C339" t="n">
-        <v>1738</v>
+        <v>910</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>0.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="340">
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>23.5</v>
+        <v>33.3</v>
       </c>
       <c r="C340" t="n">
-        <v>824</v>
+        <v>2293</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>1</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="341">
@@ -7582,10 +7582,10 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>8.300000000000001</v>
+        <v>21.5</v>
       </c>
       <c r="C341" t="n">
-        <v>971</v>
+        <v>3595</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>1.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="342">
@@ -7603,10 +7603,10 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>-6.2</v>
+        <v>-3.3</v>
       </c>
       <c r="C342" t="n">
-        <v>901</v>
+        <v>3442</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>2</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="343">
@@ -7624,18 +7624,18 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>5.7</v>
+        <v>1.4</v>
       </c>
       <c r="C343" t="n">
-        <v>48</v>
+        <v>3539</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="344">
@@ -7645,18 +7645,18 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>1.1</v>
+        <v>-2</v>
       </c>
       <c r="C344" t="n">
-        <v>73</v>
+        <v>2105</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>0</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="345">
@@ -7666,18 +7666,18 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>9.699999999999999</v>
+        <v>22.1</v>
       </c>
       <c r="C345" t="n">
-        <v>79</v>
+        <v>3162</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="346">
@@ -7687,10 +7687,10 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>30.4</v>
+        <v>21</v>
       </c>
       <c r="C346" t="n">
-        <v>2599</v>
+        <v>1676</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>0.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="347">
@@ -7708,10 +7708,10 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>23.3</v>
+        <v>12.7</v>
       </c>
       <c r="C347" t="n">
-        <v>3823</v>
+        <v>2260</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="348">
@@ -7729,10 +7729,10 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>-3.3</v>
+        <v>7.6</v>
       </c>
       <c r="C348" t="n">
-        <v>3313</v>
+        <v>3509</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>1.5</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="349">
@@ -7750,10 +7750,10 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>14.3</v>
+        <v>-0.1</v>
       </c>
       <c r="C349" t="n">
-        <v>2361</v>
+        <v>3471</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="350">
@@ -7771,18 +7771,18 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>-6.3</v>
+        <v>24.6</v>
       </c>
       <c r="C350" t="n">
-        <v>9</v>
+        <v>3363</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="351">
@@ -7792,10 +7792,10 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>46.3</v>
+        <v>16.7</v>
       </c>
       <c r="C351" t="n">
-        <v>1134</v>
+        <v>2670</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>0.5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="352">
@@ -7813,10 +7813,10 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>12.7</v>
+        <v>14.9</v>
       </c>
       <c r="C352" t="n">
-        <v>936</v>
+        <v>1445</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>1</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="353">
@@ -7834,10 +7834,10 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>13.2</v>
+        <v>20.4</v>
       </c>
       <c r="C353" t="n">
-        <v>2300</v>
+        <v>2821</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>1.5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="354">
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>14.2</v>
+        <v>21.8</v>
       </c>
       <c r="C354" t="n">
-        <v>1789</v>
+        <v>1746</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>2</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="355">
@@ -7876,10 +7876,10 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C355" t="n">
-        <v>1414</v>
+        <v>3562</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>2.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="356">
@@ -7897,18 +7897,18 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>-5.2</v>
+        <v>29.9</v>
       </c>
       <c r="C356" t="n">
-        <v>107</v>
+        <v>2215</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>0</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="357">
@@ -7918,10 +7918,10 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>30.3</v>
+        <v>14</v>
       </c>
       <c r="C357" t="n">
-        <v>1163</v>
+        <v>2468</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>0.5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="358">
@@ -7939,10 +7939,10 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>39.5</v>
+        <v>22.7</v>
       </c>
       <c r="C358" t="n">
-        <v>3344</v>
+        <v>3173</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>1</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="359">
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>20.8</v>
+        <v>5.2</v>
       </c>
       <c r="C359" t="n">
-        <v>4032</v>
+        <v>2987</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>1.5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="360">
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>12.4</v>
+        <v>26.8</v>
       </c>
       <c r="C360" t="n">
-        <v>2249</v>
+        <v>1358</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>2</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="361">
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>27</v>
+        <v>24.2</v>
       </c>
       <c r="C361" t="n">
-        <v>1345</v>
+        <v>2373</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>2.5</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>281</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4">
@@ -8069,7 +8069,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5">
@@ -8079,7 +8079,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78.09999999999999</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="6">
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -8109,7 +8109,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-18.4</v>
+        <v>-16.4</v>
       </c>
     </row>
     <row r="9">
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
